--- a/demo/configs/HeroConfig.xlsx
+++ b/demo/configs/HeroConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -22,7 +22,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>path</t>
+    <t>weapon</t>
   </si>
   <si>
     <t>element</t>
@@ -64,13 +64,13 @@
     <t>1001</t>
   </si>
   <si>
-    <t>开拓者·毁灭</t>
-  </si>
-  <si>
-    <t>毁灭</t>
-  </si>
-  <si>
-    <t>物理</t>
+    <t>炎锋·旅者</t>
+  </si>
+  <si>
+    <t>单手剑</t>
+  </si>
+  <si>
+    <t>火</t>
   </si>
   <si>
     <t>5</t>
@@ -106,123 +106,120 @@
     <t>1002</t>
   </si>
   <si>
-    <t>巡星·猎手</t>
-  </si>
-  <si>
-    <t>巡猎</t>
+    <t>湍流·猎手</t>
+  </si>
+  <si>
+    <t>弓</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>100201</t>
+  </si>
+  <si>
+    <t>100202</t>
+  </si>
+  <si>
+    <t>100203</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>惊雷·秘法</t>
+  </si>
+  <si>
+    <t>法器</t>
+  </si>
+  <si>
+    <t>雷</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>100301</t>
+  </si>
+  <si>
+    <t>100302</t>
+  </si>
+  <si>
+    <t>100303</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>冻土·壁垒</t>
+  </si>
+  <si>
+    <t>长柄武器</t>
+  </si>
+  <si>
+    <t>冰</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>100401</t>
+  </si>
+  <si>
+    <t>100402</t>
+  </si>
+  <si>
+    <t>100403</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>疾风·吟游</t>
   </si>
   <si>
     <t>风</t>
   </si>
   <si>
-    <t>980</t>
-  </si>
-  <si>
-    <t>720</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>100201</t>
-  </si>
-  <si>
-    <t>100202</t>
-  </si>
-  <si>
-    <t>100203</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>智识·星火</t>
-  </si>
-  <si>
-    <t>智识</t>
-  </si>
-  <si>
-    <t>火</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>100301</t>
-  </si>
-  <si>
-    <t>100302</t>
-  </si>
-  <si>
-    <t>100303</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>存护·壁垒</t>
-  </si>
-  <si>
-    <t>存护</t>
-  </si>
-  <si>
-    <t>冰</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>100401</t>
-  </si>
-  <si>
-    <t>100402</t>
-  </si>
-  <si>
-    <t>100403</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>丰饶·清泉</t>
-  </si>
-  <si>
-    <t>丰饶</t>
-  </si>
-  <si>
-    <t>雷</t>
-  </si>
-  <si>
     <t>1100</t>
   </si>
   <si>
@@ -244,13 +241,13 @@
     <t>1006</t>
   </si>
   <si>
-    <t>同谐·回响</t>
-  </si>
-  <si>
-    <t>同谐</t>
-  </si>
-  <si>
-    <t>量子</t>
+    <t>磐岩·重锋</t>
+  </si>
+  <si>
+    <t>双手剑</t>
+  </si>
+  <si>
+    <t>岩</t>
   </si>
   <si>
     <t>1050</t>
@@ -821,25 +818,25 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
         <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>57</v>
       </c>
       <c r="F6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" t="s">
         <v>69</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
         <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>71</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -848,13 +845,13 @@
         <v>24</v>
       </c>
       <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" t="s">
         <v>72</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>73</v>
-      </c>
-      <c r="N6" t="s">
-        <v>74</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>
@@ -862,31 +859,31 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>76</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>57</v>
       </c>
       <c r="F7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s">
         <v>79</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>80</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>81</v>
-      </c>
-      <c r="I7" t="s">
-        <v>82</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -895,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="L7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" t="s">
         <v>83</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>84</v>
-      </c>
-      <c r="N7" t="s">
-        <v>85</v>
       </c>
       <c r="O7" t="s">
         <v>28</v>
